--- a/tests/fixtures/so-ref.xlsx
+++ b/tests/fixtures/so-ref.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Exemplo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{0109A3C7-3B61-48FF-9F19-478B0662E973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -2944,10 +2944,10 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E5" dT="2026-07-13T14:05:01.39" personId="{E95E8EAA-183E-49E9-B800-72A393CDF372}" id="{13F3A532-C9D8-45E9-8F90-14493AB154A2}">
-    <text>valor p/Bruna para conta Jhon</text>
+    <text>comentario de teste</text>
   </threadedComment>
   <threadedComment ref="E12" dT="2026-05-20T14:23:38.31" personId="{E95E8EAA-183E-49E9-B800-72A393CDF372}" id="{59788B5C-0757-4D79-81A5-E1811E487993}">
-    <text>GRUPO M8 DOCUMENTOS</text>
+    <text>comentario de teste</text>
   </threadedComment>
 </ThreadedComments>
 </file>
